--- a/Squeeze_Project_Donations_v2.xlsx
+++ b/Squeeze_Project_Donations_v2.xlsx
@@ -756,7 +756,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1042,7 +1041,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1511,7 +1509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2047,40 +2045,63 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Alison Enis</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Venmo</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C26" s="9">
+      <c r="C27" s="9">
         <f>SUM(C5:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="10">
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="10">
         <f>SUM(E5:E25)</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="15" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>Est. Fees</t>
         </is>
       </c>
-      <c r="C27" s="16">
+      <c r="C28" s="16">
         <f>-E26</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="17" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Net Received</t>
         </is>
       </c>
-      <c r="C28" s="18">
+      <c r="C29" s="18">
         <f>C26+C27</f>
         <v/>
       </c>
@@ -2120,7 +2141,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2452,7 +2472,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>

--- a/Squeeze_Project_Donations_v2.xlsx
+++ b/Squeeze_Project_Donations_v2.xlsx
@@ -732,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -756,6 +756,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -968,40 +969,63 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Kevin Saliba</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" s="9">
+      <c r="C14" s="9">
         <f>SUM(C5:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="10">
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="10">
         <f>SUM(E5:E12)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="15" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Est. Fees</t>
         </is>
       </c>
-      <c r="C14" s="16">
+      <c r="C15" s="16">
         <f>-E13</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Net Received</t>
         </is>
       </c>
-      <c r="C15" s="18">
+      <c r="C16" s="18">
         <f>C13+C14</f>
         <v/>
       </c>
@@ -1533,7 +1557,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
